--- a/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,64</t>
+          <t>-1,07; 1,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,03</t>
+          <t>-1,61; 1,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,05</t>
+          <t>-0,46; 3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,48</t>
+          <t>-0,89; 1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,7</t>
+          <t>-0,53; 1,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,0</t>
+          <t>-0,92; 1,01</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,78</t>
+          <t>-2,28; 0,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,78</t>
+          <t>-1,69; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,1</t>
+          <t>-3,24; -0,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,64</t>
+          <t>-3,56; -0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,03</t>
+          <t>-2,17; -0,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,08</t>
+          <t>-2,17; 0,14</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 537,29</t>
+          <t>-88,27; 439,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,68</t>
+          <t>-93,33; 27,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,18; 43,75</t>
+          <t>-92,11; 46,47</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,06</t>
+          <t>0,31; 3,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,83</t>
+          <t>0,19; 1,73</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,67</t>
+          <t>-0,5; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,22</t>
+          <t>-0,26; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,41</t>
+          <t>-0,77; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-0,87; 0,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,34</t>
+          <t>-0,51; 0,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,5</t>
+          <t>-0,39; 0,48</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 372,18</t>
+          <t>-77,53; 524,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 698,16</t>
+          <t>-46,36; 667,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 188,45</t>
+          <t>-81,62; 184,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,21</t>
+          <t>-100,0; 94,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 108,17</t>
+          <t>-65,25; 123,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 167,65</t>
+          <t>-55,52; 164,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,87</t>
+          <t>-1,56; 1,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,03</t>
+          <t>-1,61; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,0</t>
+          <t>-0,47; 2,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,53</t>
+          <t>-1,29; 1,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,68</t>
+          <t>-0,5; 1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,01</t>
+          <t>-0,75; 1,22</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,78</t>
+          <t>-2,23; 0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,55</t>
+          <t>-1,79; 1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,06</t>
+          <t>-3,27; -0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,64</t>
+          <t>-3,79; -0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; -0,01</t>
+          <t>-2,29; -0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,14</t>
+          <t>-2,12; 0,05</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,27; 439,29</t>
+          <t>-85,63; 782,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,33; 27,32</t>
+          <t>-100,0; 55,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,11; 46,47</t>
+          <t>-91,28; 43,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,16</t>
+          <t>0,31; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,73</t>
+          <t>0,15; 1,82</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,68</t>
+          <t>-0,55; 0,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,15</t>
+          <t>-0,22; 1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,41</t>
+          <t>-0,76; 0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,15</t>
+          <t>-0,96; 0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,35</t>
+          <t>-0,45; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,48</t>
+          <t>-0,38; 0,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 524,61</t>
+          <t>-76,44; 451,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 667,12</t>
+          <t>-39,9; 705,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,62; 184,4</t>
+          <t>-80,98; 224,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,32</t>
+          <t>-100,0; 156,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 123,68</t>
+          <t>-63,35; 109,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 164,95</t>
+          <t>-55,78; 188,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,03</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,63</t>
+          <t>-0,46; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,04</t>
+          <t>-0,9; 1,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,76</t>
+          <t>-1,07; 1,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,48</t>
+          <t>-1,62; 1,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,9</t>
+          <t>-0,51; 1,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,22</t>
+          <t>-0,94; 1,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>198,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-4,98%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>198,93%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,73</t>
+          <t>-3,54; -0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,85</t>
+          <t>-3,55; -0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,1</t>
+          <t>-2,26; 0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,64</t>
+          <t>-1,71; 1,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -0,05</t>
+          <t>-2,32; -0,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,05</t>
+          <t>-2,09; 0,08</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-81,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-48,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-4,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-81,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,63; 782,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,8; 537,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,0</t>
+          <t>-100,0; 29,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,28; 43,0</t>
+          <t>-91,18; 43,75</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,12</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,08</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,31; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,82</t>
+          <t>0,22; 1,83</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,69</t>
+          <t>-0,78; 0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,24</t>
+          <t>-0,95; 0,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,42</t>
+          <t>-0,57; 0,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,19</t>
+          <t>-0,27; 1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,32</t>
+          <t>-0,49; 0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,49</t>
+          <t>-0,39; 0,5</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-23,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-53,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>87,18%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-23,05%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-53,89%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 451,27</t>
+          <t>-80,72; 188,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 705,62</t>
+          <t>-100,0; 121,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 224,47</t>
+          <t>-77,98; 372,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,29</t>
+          <t>-46,07; 698,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 109,5</t>
+          <t>-62,78; 108,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 188,55</t>
+          <t>-56,52; 167,65</t>
         </is>
       </c>
     </row>
